--- a/simple_quote.xlsx
+++ b/simple_quote.xlsx
@@ -46,8 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,131 +467,174 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Q-2025-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>深圳 (Shenzhen)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>洛杉矶 (Los Angeles)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>COSCO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>20'GP</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>含燃油附加费，不含目的港杂费</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Q-2025-089 / 手写改 090</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>盐田 YANTIAN（CNSHA? 实际盐田 YICT）</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Hamburg / via Rotterdam
+最终目的港：DEHAM</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>EMC 长荣
+EVER GLORY V.025E
+OA联盟</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>20'GP / 40'HQ 均可，高柜优先</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>USD 1650 + BAF 275 + PSS 150
+(all-in 约 2075)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>有效期至 09/15/2026
+ETD 9.8 / ETA 10.3</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>25-30天
+新加坡中转 3-5天</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>含 THC/ORC，不含目的港 DTHC
+周三截关 周五开船
+超重费 USD50/20'</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Q-2025-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>上海 (Shanghai)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>鹿特丹 (Rotterdam)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>40'HQ</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2650</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>28</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>直航，含旺季附加费</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>青岛-纽约线 2025-090</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>青岛 QINGDAO (CY)
+可接郑州/西安 铁路</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>NEW YORK / SAVANNAH
+目的港码头 APMT / GCT</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>HPL 赫伯罗特
+HAMBURG EXPRESS 0DB6FE
+船期：二四六</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>40'HC (40英尺高柜)
+也接受 45'HC</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>3100 (all in)
+含 FAF/CAF, 不含 D&amp;D</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-20 ~ 2026-10-10
+滚装有效，以订舱为准</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>35天
+中转釜山 + 巴拿马运河</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>PSS USD 250/40'
+ERS (紧急燃油) USD 80/柜
+超重费 USD75/柜 (货重&gt;22t)
+限重 23mt</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Q-2025-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>宁波 (Ningbo)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>悉尼 (Sydney)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ONE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>40'GP</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>每周三截关，需提前订舱</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AKL-0926 / 待确认</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>上海 SHANGHAI (CNSSA?)
+实际上海外高桥</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>AUCKLAND, NZ
+可转运 Christchurch / Wellington</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>MSK 马士基</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>20'RF (冷藏)
+如需 40'NOR 另询</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>USD 2250 + DOC 50
++ 币值调整 CAF 1.5%
+汇率按 7.25 暂估</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>26-Sep-2026
+MAERSK HORSBURGH 346S
+ETD 9.26</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>16-18天
+新加坡中转 2天
+周日截关 周三开</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>免堆 7天
+冷柜插电 USD120/柜
+洗箱费实报实销
+舱位紧张需提前10天订</t>
         </is>
       </c>
     </row>
